--- a/day-1/day-1.xlsx
+++ b/day-1/day-1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Note" sheetId="1" state="visible" r:id="rId2"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="88">
   <si>
     <t xml:space="preserve">1. Khi có vấn đề, DA sẽ phải hiểu data, tự đặt ra các câu hỏi để giải quyết vấn đề, vì sao giảm/tăng, giảm/tăng so với thời gian nào, nó giảm/tăng bao nhiêu,...tìm ra nguyên nhân chứ không chỉ query data</t>
   </si>
@@ -259,16 +259,42 @@
   </si>
   <si>
     <t xml:space="preserve">8. Từ bảng trên, hãy đưa ra 5 business questions mà một Data Analyst có thể phân tích.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. Câu hỏi tổng kết. Có bảng:  order_items  với granularity:  one row = one product in one order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager hỏi:  "Có bao nhiêu orders và tổng revenue là bao nhiêu?"  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo bạn, có vấn đề gì nếu Data Analyst chỉ dùng:  COUNT(order_id)  để đếm số order?  Và cần suy nghĩ thế nào để tính đúng?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">một row ở đây biểu diễn một product, trong 1 order nên nếu order nhiều product thì sẽ có rất nhiều dòng, để tính đúng phải đếm id nhưng đếm distinct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT     COUNT(DISTINCT order_id) AS total_orders,     SUM(quantity * price) AS total_revenue FROM order_items;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -323,10 +349,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFFF4000"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -384,7 +412,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -425,19 +453,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -856,7 +896,7 @@
       <c r="G16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H16" s="10" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">SUMIF(G15:G20,"S",E15:E20)</f>
         <v>28000000</v>
       </c>
@@ -942,7 +982,7 @@
       <c r="B24" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -962,7 +1002,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -971,12 +1011,12 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
         <v>63</v>
       </c>
     </row>
@@ -986,7 +1026,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
         <v>65</v>
       </c>
     </row>
@@ -996,7 +1036,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="11" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1006,12 +1046,12 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="11" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1021,7 +1061,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="11" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1031,7 +1071,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="11" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1039,12 +1079,12 @@
       <c r="A15" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="11" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1054,8 +1094,101 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="11" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
